--- a/Output.xlsx
+++ b/Output.xlsx
@@ -751,265 +751,265 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Unnamed: 15</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
+          <t>Total Cost</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>14927.83098039216</v>
+      </c>
+      <c r="C14" t="n">
+        <v>1978.21</v>
+      </c>
+      <c r="D14" t="n">
+        <v>90.45</v>
+      </c>
+      <c r="E14" t="n">
+        <v>39260.85190336299</v>
+      </c>
+      <c r="F14" t="n">
+        <v>90.45</v>
+      </c>
+      <c r="G14" t="n">
+        <v>217687</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Total Cost</t>
+          <t>Total cost in Crores</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>14927.83098039216</v>
+        <v>149278309803.9216</v>
       </c>
       <c r="C15" t="n">
-        <v>1978.21</v>
+        <v>19782100000</v>
       </c>
       <c r="D15" t="n">
-        <v>90.45</v>
+        <v>904500000</v>
       </c>
       <c r="E15" t="n">
-        <v>39260.85190336299</v>
+        <v>392608519033.6298</v>
       </c>
       <c r="F15" t="n">
-        <v>90.45</v>
+        <v>904500000</v>
       </c>
       <c r="G15" t="n">
-        <v>217687</v>
+        <v>2176870000000</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Total cost in Crores</t>
+          <t>Cost Per employee</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>149278309803.9216</v>
+        <v>6864777.278924542</v>
       </c>
       <c r="C16" t="n">
-        <v>19782100000</v>
+        <v>3822122.222222222</v>
       </c>
       <c r="D16" t="n">
-        <v>904500000</v>
+        <v>325025.7142857143</v>
       </c>
       <c r="E16" t="n">
-        <v>392608519033.6298</v>
+        <v>8800036.691542311</v>
       </c>
       <c r="F16" t="n">
-        <v>904500000</v>
+        <v>325025.7142857143</v>
       </c>
       <c r="G16" t="n">
-        <v>2176870000000</v>
+        <v>45119257.95053004</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Cost Per employee</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>6864777.278924542</v>
+        <v>17294547842.46349</v>
       </c>
       <c r="C17" t="n">
-        <v>3822122.222222222</v>
+        <v>2350964823.909927</v>
       </c>
       <c r="D17" t="n">
-        <v>325025.7142857143</v>
+        <v>94669874.97828496</v>
       </c>
       <c r="E17" t="n">
-        <v>8800036.691542311</v>
+        <v>45675253121.14748</v>
       </c>
       <c r="F17" t="n">
-        <v>325025.7142857143</v>
+        <v>94669874.97828496</v>
       </c>
       <c r="G17" t="n">
-        <v>45119257.95053004</v>
+        <v>252880713467.3628</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>Research</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>16960651296.39663</v>
+        <v>16292854449.32817</v>
       </c>
       <c r="C18" t="n">
-        <v>2396175685.908195</v>
+        <v>2086520118.071798</v>
       </c>
       <c r="D18" t="n">
-        <v>95710203.27474964</v>
+        <v>95235026.71795635</v>
       </c>
       <c r="E18" t="n">
-        <v>44742439388.29288</v>
+        <v>42122543771.1913</v>
       </c>
       <c r="F18" t="n">
-        <v>95710203.27474964</v>
+        <v>95235026.71795635</v>
       </c>
       <c r="G18" t="n">
-        <v>250376944027.0919</v>
+        <v>217891129775.5922</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>R/D</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>16622131749.76862</v>
+        <v>16324526900.99283</v>
       </c>
       <c r="C19" t="n">
-        <v>2242233954.475753</v>
+        <v>2368215031.432388</v>
       </c>
       <c r="D19" t="n">
-        <v>94428787.52746184</v>
+        <v>107006417.1810986</v>
       </c>
       <c r="E19" t="n">
-        <v>44564828216.54002</v>
+        <v>44250907393.85338</v>
       </c>
       <c r="F19" t="n">
-        <v>94428787.52746184</v>
+        <v>107006417.1810986</v>
       </c>
       <c r="G19" t="n">
-        <v>246006114262.7654</v>
+        <v>259918079061.7178</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>Support</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>16131211412.53764</v>
+        <v>16559603908.41614</v>
       </c>
       <c r="C20" t="n">
-        <v>2166954983.639631</v>
+        <v>2118722431.748974</v>
       </c>
       <c r="D20" t="n">
-        <v>104365597.9179473</v>
+        <v>97755976.28077452</v>
       </c>
       <c r="E20" t="n">
-        <v>42836377504.15679</v>
+        <v>43870229876.26225</v>
       </c>
       <c r="F20" t="n">
-        <v>104365597.9179473</v>
+        <v>97755976.28077452</v>
       </c>
       <c r="G20" t="n">
-        <v>247995231398.3362</v>
+        <v>252181925032.4878</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Support</t>
+          <t>Compliance</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>15587022511.18103</v>
+        <v>16401987311.69851</v>
       </c>
       <c r="C21" t="n">
-        <v>2118722431.748974</v>
+        <v>2352809081.990935</v>
       </c>
       <c r="D21" t="n">
-        <v>101861518.7615661</v>
+        <v>90799654.41317728</v>
       </c>
       <c r="E21" t="n">
-        <v>39444734606.20055</v>
+        <v>43095384861.82637</v>
       </c>
       <c r="F21" t="n">
-        <v>101861518.7615661</v>
+        <v>90799654.41317728</v>
       </c>
       <c r="G21" t="n">
-        <v>214116728801.1689</v>
+        <v>232780376893.7498</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Legal / Compliance</t>
+          <t>Maintanience</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>16541059781.27092</v>
+        <v>16393094475.08712</v>
       </c>
       <c r="C22" t="n">
-        <v>2359018973.514367</v>
+        <v>2108116245.585072</v>
       </c>
       <c r="D22" t="n">
-        <v>94747465.47461976</v>
+        <v>94422586.03229274</v>
       </c>
       <c r="E22" t="n">
-        <v>44154381756.66238</v>
+        <v>42803934395.57755</v>
       </c>
       <c r="F22" t="n">
-        <v>94747465.47461976</v>
+        <v>94422586.03229274</v>
       </c>
       <c r="G22" t="n">
-        <v>247032236703.5712</v>
+        <v>234349361879.9013</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Maintanience</t>
+          <t>Customer Service</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>15549694101.38873</v>
+        <v>16710318804.43923</v>
       </c>
       <c r="C23" t="n">
-        <v>2043582074.801855</v>
+        <v>2243978871.545849</v>
       </c>
       <c r="D23" t="n">
-        <v>105856122.500161</v>
+        <v>97074293.06779419</v>
       </c>
       <c r="E23" t="n">
-        <v>39934202030.43691</v>
+        <v>44571076417.89394</v>
       </c>
       <c r="F23" t="n">
-        <v>105856122.500161</v>
+        <v>97074293.06779419</v>
       </c>
       <c r="G23" t="n">
-        <v>220146370250.8164</v>
+        <v>253513141946.8837</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Customer Service</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>17502114631.98227</v>
-      </c>
-      <c r="C24" t="n">
-        <v>2401057392.554059</v>
-      </c>
-      <c r="D24" t="n">
-        <v>111532166.5034231</v>
-      </c>
-      <c r="E24" t="n">
-        <v>47168127161.79469</v>
-      </c>
-      <c r="F24" t="n">
-        <v>111532166.5034231</v>
-      </c>
-      <c r="G24" t="n">
-        <v>265940256748.2016</v>
-      </c>
+          <t>Unnamed: 25</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
